--- a/Timeline_Viet_Anh_Class.xlsx
+++ b/Timeline_Viet_Anh_Class.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -842,30 +842,26 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
+          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>UAT 1 cơ sở + review bảo mật độc lập của IT trường</t>
+          <t>Điểm danh + cửa sổ giờ (đúng giờ/muộn/vắng) + trưởng điểm danh</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>⬜ Chưa làm</t>
+        <v>5</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>✅ Xong</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>cần nhà trường bố trí</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -875,11 +871,11 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Điểm danh + cửa sổ giờ (đúng giờ/muộn/vắng) + trưởng điểm danh</t>
+          <t>Check-in cảm xúc (cổng IP) + bảng cảm xúc lớp cho GVCN</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
@@ -887,7 +883,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
     </row>
@@ -899,7 +895,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Check-in cảm xúc (cổng IP) + bảng cảm xúc lớp cho GVCN</t>
+          <t>Thời khoá biểu + ngoại lệ theo ngày (huỷ/dời/dạy thay)</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -923,11 +919,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Thời khoá biểu + ngoại lệ theo ngày (huỷ/dời/dạy thay)</t>
+          <t>Báo bài</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
@@ -935,7 +931,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
     </row>
@@ -947,7 +943,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Báo bài</t>
+          <t>Học bạ</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -971,7 +967,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Học bạ</t>
+          <t>Liên lạc (nhắn tin GVCN ↔ phụ huynh)</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -995,11 +991,11 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Liên lạc (nhắn tin GVCN ↔ phụ huynh)</t>
+          <t>Thực đơn</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
@@ -1007,7 +1003,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
     </row>
@@ -1019,7 +1015,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Thực đơn</t>
+          <t>Ảnh lớp (bìa lớp qua Storage)</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -1043,11 +1039,11 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ảnh lớp (bìa lớp qua Storage)</t>
+          <t>Thông báo in-app</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
@@ -1055,7 +1051,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
     </row>
@@ -1067,7 +1063,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Thông báo in-app</t>
+          <t>Báo cáo phụ huynh theo tuần (điểm danh + WIG + chiêm nghiệm)</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Báo cáo phụ huynh theo tuần (điểm danh + WIG + chiêm nghiệm)</t>
+          <t>Báo cáo cơ sở cho BGH (xếp hạng + điểm danh mọi lớp)</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -1110,16 +1106,16 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
+          <t>WF3 · Lõi 4DX (WIG)</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Báo cáo cơ sở cho BGH (xếp hạng + điểm danh mọi lớp)</t>
+          <t>WIG lớp năm→tháng→tuần + chỉnh nhịp (cô kéo lại mốc)</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
@@ -1127,7 +1123,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
     </row>
@@ -1139,11 +1135,11 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>WIG lớp năm→tháng→tuần + chỉnh nhịp (cô kéo lại mốc)</t>
+          <t>Việc của lớp (lead measure, unit_per_tick)</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
@@ -1151,7 +1147,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
     </row>
@@ -1163,11 +1159,11 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Việc của lớp (lead measure, unit_per_tick)</t>
+          <t>Mục tiêu cá nhân của em: đặt/duyệt/cửa sổ 1 ngày/đặt hộ</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -1175,9 +1171,13 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>migration 0100–0102</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1187,11 +1187,11 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Mục tiêu cá nhân của em: đặt/duyệt/cửa sổ 1 ngày/đặt hộ</t>
+          <t>Tick hằng ngày (số lần/tuần = số thứ đã chọn)</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
@@ -1199,11 +1199,11 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>migration 0100–0102</t>
+          <t>migration 0103</t>
         </is>
       </c>
     </row>
@@ -1215,11 +1215,11 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Tick hằng ngày (số lần/tuần = số thứ đã chọn)</t>
+          <t>Bảng điểm cá nhân + thi đua lớp + xếp hạng đa cấp</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
@@ -1227,13 +1227,9 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>migration 0103</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1243,7 +1239,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Bảng điểm cá nhân + thi đua lớp + xếp hạng đa cấp</t>
+          <t>Phòng họp WIG + cảnh báo lệch nhịp</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -1267,11 +1263,11 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Phòng họp WIG + cảnh báo lệch nhịp</t>
+          <t>Biên bản họp cá nhân Coach × Buddy</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
@@ -1279,7 +1275,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
     </row>
@@ -1291,7 +1287,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Biên bản họp cá nhân Coach × Buddy</t>
+          <t>Buddy 4DX là LLM (DeepSeek qua OpenRouter)</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -1315,11 +1311,11 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Buddy 4DX là LLM (DeepSeek qua OpenRouter)</t>
+          <t>Sổ của con (nhật ký riêng, chỉ em viết)</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
@@ -1327,7 +1323,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
     </row>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Sổ của con (nhật ký riêng, chỉ em viết)</t>
+          <t>Bạn đồng hành hằng tuần — ghép cặp tự động ở phòng họp, tránh lặp bạn tuần trước</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -1353,51 +1349,27 @@
       <c r="E33" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>migration 0104, lib/buddy-pair.ts</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Bạn đồng hành hằng tuần — ghép cặp tự động ở phòng họp, tránh lặp bạn tuần trước</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>migration 0104, lib/buddy-pair.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="n"/>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>TỔNG</t>
         </is>
       </c>
-      <c r="C35" s="10">
-        <f>SUM(C5:C34)</f>
-      </c>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="11">
-        <f>SUM(E5:E34)</f>
-      </c>
-      <c r="F35" s="8" t="n"/>
+      <c r="C34" s="10">
+        <f>SUM(C5:C33)</f>
+      </c>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="11">
+        <f>SUM(E5:E33)</f>
+      </c>
+      <c r="F34" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1410,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1429,7 +1401,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>% HOÀN THÀNH:  98%   ( 98 / 100 )  ·  3 workflow, 30 đầu việc</t>
+          <t>% HOÀN THÀNH:  100%   ( 98 / 98 )  ·  3 workflow, 29 đầu việc</t>
         </is>
       </c>
     </row>
@@ -1462,13 +1434,13 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>28</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.9333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1516,7 +1488,7 @@
         <f>SUM(C6:C8)</f>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1600,17 +1572,17 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>WF2 · Nhịp hằng ngày (11/11) và WF3 · Lõi 4DX (10/10, sau khi buddy ghép cặp tự động xong 12/08).</t>
+          <t>WF1 · Nền tảng (8/8), WF2 · Nhịp hằng ngày (11/11), WF3 · Lõi 4DX (10/10) — không còn mục nào treo.</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>WF1 còn 1 mục chờ nhà trường (UAT/review IT) — không nằm trong tay đội dev</t>
+          <t>buddy ghép cặp tự động (0104) là mục cuối, xong 12/08</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1594,12 @@
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>30 đầu việc trên 3 workflow, tính theo trọng số cộng đúng 100.</t>
+          <t>29 đầu việc trên 3 workflow, tính theo trọng số cộng đúng 100.</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
@@ -1637,29 +1609,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>Còn lại → 100%</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Đúng một mục: UAT 1 cơ sở + review bảo mật độc lập của IT trường (WF1) — cần nhà trường bố trí người và thời gian, không phải việc code.</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>chỉ còn WF1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Chú giải: ✅ Xong=100% trọng số · ⬜ Chưa làm=0%. Trọng số mỗi mục do người phụ trách ước lượng độ lớn tương đối (S/M/L gộp vào con số), không phải giờ công.</t>
         </is>
@@ -1668,7 +1618,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A11:D11"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D8">

--- a/Timeline_Viet_Anh_Class.xlsx
+++ b/Timeline_Viet_Anh_Class.xlsx
@@ -590,786 +590,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VIET ANH CLASS — TIMELINE &amp; CHECKLIST (chốt lại theo 3 workflow, 2026-08-12)</t>
+          <t>VIET ANH CLASS — TIMELINE THEO GIAI ĐOẠN VÒNG ĐỜI (chốt 2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bản 2026-07-23 tính theo TUẦN, không khớp KPI theo đầu ra. Bản này tính theo WORKFLOW: một luồng nghiệp vụ khép kín, một vai làm được từ đầu tới cuối, demo được độc lập. Trọng số % cộng đúng 100.</t>
+          <t>Một giai đoạn chỉ tính là ĐÃ QUA khi sống đủ ≥7 ngày — không tính theo số đầu việc hay trọng số %. Demo → Hoàn thiện → Test &amp; feedback → Go-live.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Giai đoạn</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mục</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Trọng số %</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>Số ngày</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Ngưỡng ≥7 ngày</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Trạng thái</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Hoàn thành %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Nội dung chính</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Đăng nhập (Google SSO + magic link) + phân vai 6 vai</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
+          <t>① Demo</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Đạt (≥7)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>✅ Đã qua</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Dựng khung app, đăng nhập, điểm danh, WIG/lead cấp lớp, scoreboard, họp WIG, phân quyền, báo cáo — bản chốt 23/07 (118 đầu việc, 92%).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Quản trị: cơ sở→khối→lớp liên cấp, người dùng, ghi danh/chuyển/rời lớp</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>② Hoàn thiện tính năng</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Đạt (≥7)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>✅ Đã qua</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Cắm SSO thật, vá bảo mật (RLS/audit), hạ tầng deploy VPS+CI/CD, thêm báo bài/học bạ/liên lạc/thực đơn/ảnh lớp, dựng lại trang quản trị, audit mobile, sổ tay vận hành cho đợt thử 30 người.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>RLS bảo mật toàn app (6 vai) + audit log thao tác admin</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+          <t>③ Test &amp; nhận feedback</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>đang chạy</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Chưa (2 ngày nữa)</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>🔶 Đang chạy — còn 2 ngày nữa</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Đợt thử thật, sửa theo phản hồi trực tiếp: dựng lại mô hình WIG cá nhân (0100–0103), bạn đồng hành tự động (0104), sửa chữ khó hiểu, chữa lỗi số liệu (lead measure) người thử bắt được.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Danh mục môn chuẩn + phân công giáo viên bộ môn</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Song ngữ (next-intl) + design system + audit mobile/a11y</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Bộ kiểm tự động (47 script) chạy thẳng lên production</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Hạ tầng deploy VPS + CI/CD (Coolify/GHCR) + giám sát</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Google SSO thật — nút, callback, giới hạn miền email đang chạy trên production</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Điểm danh + cửa sổ giờ (đúng giờ/muộn/vắng) + trưởng điểm danh</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Check-in cảm xúc (cổng IP) + bảng cảm xúc lớp cho GVCN</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Thời khoá biểu + ngoại lệ theo ngày (huỷ/dời/dạy thay)</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Báo bài</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Học bạ</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Liên lạc (nhắn tin GVCN ↔ phụ huynh)</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Thực đơn</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Ảnh lớp (bìa lớp qua Storage)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Thông báo in-app</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Báo cáo phụ huynh theo tuần (điểm danh + WIG + chiêm nghiệm)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Báo cáo cơ sở cho BGH (xếp hạng + điểm danh mọi lớp)</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>WIG lớp năm→tháng→tuần + chỉnh nhịp (cô kéo lại mốc)</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Việc của lớp (lead measure, unit_per_tick)</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Mục tiêu cá nhân của em: đặt/duyệt/cửa sổ 1 ngày/đặt hộ</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>migration 0100–0102</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Tick hằng ngày (số lần/tuần = số thứ đã chọn)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>migration 0103</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Bảng điểm cá nhân + thi đua lớp + xếp hạng đa cấp</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Phòng họp WIG + cảnh báo lệch nhịp</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Biên bản họp cá nhân Coach × Buddy</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Buddy 4DX là LLM (DeepSeek qua OpenRouter)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Sổ của con (nhật ký riêng, chỉ em viết)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Bạn đồng hành hằng tuần — ghép cặp tự động ở phòng họp, tránh lặp bạn tuần trước</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>✅ Xong</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>migration 0104, lib/buddy-pair.ts</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>TỔNG</t>
-        </is>
-      </c>
-      <c r="C34" s="10">
-        <f>SUM(C5:C33)</f>
-      </c>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="11">
-        <f>SUM(E5:E33)</f>
-      </c>
-      <c r="F34" s="8" t="n"/>
+          <t>④ Go-live (học sinh dùng thật liên tục)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr"/>
+      <c r="C8" s="16" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>⬜ Chưa bắt đầu</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Chưa bắt đầu — chỉ tính khi học sinh dùng thật, liên tục, không phải đợt thử có kiểm soát.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1385,7 +803,7 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
@@ -1394,50 +812,50 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>BẢNG ĐIỀU KHIỂN TIẾN ĐỘ — 3 WORKFLOW</t>
+          <t>BẢNG ĐIỀU KHIỂN — TIẾN ĐỘ THEO GIAI ĐOẠN</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>% HOÀN THÀNH:  100%   ( 98 / 98 )  ·  3 workflow, 29 đầu việc</t>
+          <t>2/4 giai đoạn đã qua ngưỡng ≥7 ngày · đang ở "③ Test &amp; nhận feedback" (ngày thứ 5)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Workflow</t>
+          <t>Giai đoạn</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Trọng số %</t>
+          <t>Số ngày</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Đã xong %</t>
+          <t>Ngưỡng</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>% workflow</t>
+          <t>% ngưỡng</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng &amp; Vận hành</t>
+          <t>① Demo</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>1</v>
@@ -1446,14 +864,14 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>WF2 · Nhịp hằng ngày &amp; Tiện ích lớp</t>
+          <t>② Hoàn thiện tính năng</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>1</v>
@@ -1462,39 +880,39 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>WF3 · Lõi 4DX (WIG)</t>
+          <t>③ Test &amp; nhận feedback</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>TỔNG</t>
-        </is>
-      </c>
-      <c r="B9" s="10">
-        <f>SUM(B6:B8)</f>
-      </c>
-      <c r="C9" s="22">
-        <f>SUM(C6:C8)</f>
-      </c>
-      <c r="D9" s="23" t="n">
-        <v>1</v>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>④ Go-live (học sinh dùng thật liên tục)</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>ĐÁNH GIÁ — VÌ SAO CHỐT LẠI THÀNH 3 WORKFLOW</t>
+          <t>VÌ SAO ĐỔI CÁCH TÍNH</t>
         </is>
       </c>
     </row>
@@ -1523,95 +941,95 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Vì sao bỏ tính theo tuần</t>
+          <t>Vì sao bỏ tính theo đầu việc</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>4 tuần</t>
+          <t>29/29</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bản 23/07 tính theo tuần: 1 workflow = 1 tuần. Đơn vị thời gian phạt tốc độ — làm nhanh thì KPI thấp, và app đã chạy 4 tuần với tốc độ đổi rất khác nhau giữa các tuần.</t>
+          <t>Bản trước đó (3 workflow theo trọng số đầu việc) đạt 100% dù app còn đang trong đợt thử — số đẹp nhưng không nói được "đã sẵn sàng cho học sinh dùng thật chưa". Chủ dự án bác bỏ 12/08/2026.</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>153 commit không đều theo tuần</t>
+          <t>đếm việc đã LÀM, không đếm việc đã ỔN ĐỊNH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>Định nghĩa 1 workflow</t>
+          <t>Luật mới</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>3 cái</t>
+          <t>≥7 ngày</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Một luồng nghiệp vụ khép kín, một vai làm được từ đầu tới cuối, demo/nghiệm thu độc lập được.</t>
+          <t>Một giai đoạn chỉ "qua" khi sống đủ số ngày tối thiểu — ép mỗi giai đoạn phải chịu được thời gian thật, không chỉ một lần bấm là xong.</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>WF1 nền tảng · WF2 nhịp hằng ngày · WF3 lõi 4DX</t>
+          <t>demo → hoàn thiện → test &amp; feedback → go-live</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>Workflow đã xong hoàn toàn</t>
+          <t>Đang đứng ở đâu</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>③ Test &amp; nhận feedback</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>WF1 · Nền tảng (8/8), WF2 · Nhịp hằng ngày (11/11), WF3 · Lõi 4DX (10/10) — không còn mục nào treo.</t>
+          <t>Ngày thứ 5/7 của giai đoạn Test &amp; nhận feedback (bắt đầu 2026-08-08).</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>buddy ghép cặp tự động (0104) là mục cuối, xong 12/08</t>
+          <t>còn 2 ngày nữa mới đạt ngưỡng</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>Tổng tiến độ</t>
+          <t>Go-live thật</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Chưa bắt đầu</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>29 đầu việc trên 3 workflow, tính theo trọng số cộng đúng 100.</t>
+          <t>Chỉ tính khi học sinh dùng thật, liên tục, không phải đợt thử có kiểm soát — và cũng cần sống đủ ≥7 ngày mới qua.</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>không gồm phần bản 23/07 đã lỗi thời</t>
+          <t>chưa có mốc bắt đầu</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>Chú giải: ✅ Xong=100% trọng số · ⬜ Chưa làm=0%. Trọng số mỗi mục do người phụ trách ước lượng độ lớn tương đối (S/M/L gộp vào con số), không phải giờ công.</t>
+          <t>Chú giải: ✅ Đã qua ngưỡng · 🔶 Đang chạy · ⬜ Chưa bắt đầu. "Số ngày" của giai đoạn đang chạy tính tới hôm nay, tăng dần mỗi ngày cho tới khi chuyển giai đoạn kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1039,7 @@
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A11:D11"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D8">
+  <conditionalFormatting sqref="D6:D9">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/Timeline_Viet_Anh_Class.xlsx
+++ b/Timeline_Viet_Anh_Class.xlsx
@@ -590,29 +590,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="76" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VIET ANH CLASS — TIMELINE THEO GIAI ĐOẠN VÒNG ĐỜI (chốt 2026-08-12)</t>
+          <t>VIET ANH CLASS — TIMELINE THEO GIAI ĐOẠN VÒNG ĐỜI (chốt 2026-08-12, v2)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Một giai đoạn chỉ tính là ĐÃ QUA khi sống đủ ≥7 ngày — không tính theo số đầu việc hay trọng số %. Demo → Hoàn thiện → Test &amp; feedback → Go-live.</t>
+          <t>3 giai đoạn: Demo → Xây &amp; thử liên tục → Go-live. Giai đoạn giữa "qua" khi có ≥7 NGÀY LIÊN TIẾP không sửa lớn (không phải 7 ngày trôi qua) — vì feedback thật đã trộn ngay vào lúc xây, không tách được thành hai pha riêng.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Ngưỡng ≥7 ngày</t>
+          <t>Ngưỡng</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>Đạt (≥7)</t>
+          <t>9/7 ngày</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>② Hoàn thiện tính năng</t>
+          <t>② Xây &amp; thử liên tục</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -703,89 +703,52 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>đang chạy</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>Đạt (≥7)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>✅ Đã qua</t>
+          <t>chuỗi yên: 0/7 ngày</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>🔶 Đang chạy — sửa lớn gần nhất 2026-08-12, cần 7 ngày yên nữa</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Cắm SSO thật, vá bảo mật (RLS/audit), hạ tầng deploy VPS+CI/CD, thêm báo bài/học bạ/liên lạc/thực đơn/ảnh lớp, dựng lại trang quản trị, audit mobile, sổ tay vận hành cho đợt thử 30 người.</t>
+          <t>Hoàn thiện + test + nhận feedback GỘP LÀM MỘT — thực tế feedback đã có ngay từ trong lúc xây (vd "7 tính năng người thử đề xuất" 30/07). Ngưỡng không đếm ngày trôi qua mà đếm CHUỖI NGÀY LIÊN TIẾP không có sửa lớn — tín hiệu ổn định thật.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>③ Test &amp; nhận feedback</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>đang chạy</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>③ Go-live (học sinh dùng thật liên tục)</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr"/>
+      <c r="C7" s="16" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr"/>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>Chưa (2 ngày nữa)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>🔶 Đang chạy — còn 2 ngày nữa</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>⬜ Chưa bắt đầu</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Đợt thử thật, sửa theo phản hồi trực tiếp: dựng lại mô hình WIG cá nhân (0100–0103), bạn đồng hành tự động (0104), sửa chữ khó hiểu, chữa lỗi số liệu (lead measure) người thử bắt được.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>④ Go-live (học sinh dùng thật liên tục)</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>⬜ Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu — chỉ tính khi học sinh dùng thật, liên tục, không phải đợt thử có kiểm soát.</t>
+          <t>Mở khi giai đoạn ② đạt chuỗi yên ≥7 ngày. Chỉ tính khi học sinh dùng thật, liên tục — và cũng cần sống đủ ≥7 ngày mới qua.</t>
         </is>
       </c>
     </row>
@@ -800,26 +763,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>BẢNG ĐIỀU KHIỂN — TIẾN ĐỘ THEO GIAI ĐOẠN</t>
+          <t>BẢNG ĐIỀU KHIỂN — CHUỖI NGÀY YÊN ỔN</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>2/4 giai đoạn đã qua ngưỡng ≥7 ngày · đang ở "③ Test &amp; nhận feedback" (ngày thứ 5)</t>
+          <t>Chuỗi yên hiện tại: 0/7 ngày · sửa lớn gần nhất: 2026-08-12 · 1/3 giai đoạn đã qua</t>
         </is>
       </c>
     </row>
@@ -864,182 +827,150 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>② Hoàn thiện tính năng</t>
+          <t>② Chuỗi yên (không phải số ngày chạy)</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>7</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>③ Test &amp; nhận feedback</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>④ Go-live (học sinh dùng thật liên tục)</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>0</v>
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>VÌ SAO GỘP ②+③ VÀ ĐỔI Ý NGHĨA NGƯỠNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Mức</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>VÌ SAO ĐỔI CÁCH TÍNH</t>
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Vì sao gộp Hoàn thiện + Test</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>30/07</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Bản 4-giai-đoạn tách riêng "Hoàn thiện" và "Test &amp; feedback" ở mốc 08/08 — nhưng feedback thật đã có từ 30/07 ("7 tính năng người thử đề xuất"), NẰM TRONG giai đoạn tưởng là chỉ-xây. Mốc tách không có thật.</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>chủ dự án bắt đúng 12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Mức</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Nội dung</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Ngưỡng đổi ý nghĩa</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>7 ngày yên</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Không đếm ngày trôi qua kể từ lúc bắt đầu giai đoạn (số đó tăng đều dù vẫn đang sửa) — đếm CHUỖI NGÀY LIÊN TIẾP không có sửa lớn nào. Reset về 0 mỗi lần có sửa mã/CSDL.</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>sửa lớn = đổi app/**, components/**, lib/**, supabase/migrations/** — không tính đổi *.xlsx/*.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Vì sao bỏ tính theo đầu việc</t>
+          <t>Đang đứng ở đâu</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>29/29</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bản trước đó (3 workflow theo trọng số đầu việc) đạt 100% dù app còn đang trong đợt thử — số đẹp nhưng không nói được "đã sẵn sàng cho học sinh dùng thật chưa". Chủ dự án bác bỏ 12/08/2026.</t>
+          <t>Sửa lớn gần nhất 2026-08-12 (bạn đồng hành hằng tuần, migration 0104). Chuỗi yên bắt đầu tính lại từ ngày sau đó.</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>đếm việc đã LÀM, không đếm việc đã ỔN ĐỊNH</t>
+          <t>còn 7 ngày liên tiếp không sửa lớn nữa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>Luật mới</t>
+          <t>Go-live thật</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>≥7 ngày</t>
+          <t>Chưa bắt đầu</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Một giai đoạn chỉ "qua" khi sống đủ số ngày tối thiểu — ép mỗi giai đoạn phải chịu được thời gian thật, không chỉ một lần bấm là xong.</t>
+          <t>Chỉ mở khi giai đoạn ② đạt chuỗi yên ≥7 — và bản thân go-live cũng cần sống đủ ≥7 ngày mới qua.</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>demo → hoàn thiện → test &amp; feedback → go-live</t>
+          <t>gate kép: ổn định trước, rồi mới đo go-live</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>Đang đứng ở đâu</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>③ Test &amp; nhận feedback</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Ngày thứ 5/7 của giai đoạn Test &amp; nhận feedback (bắt đầu 2026-08-08).</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>còn 2 ngày nữa mới đạt ngưỡng</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Go-live thật</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ tính khi học sinh dùng thật, liên tục, không phải đợt thử có kiểm soát — và cũng cần sống đủ ≥7 ngày mới qua.</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>chưa có mốc bắt đầu</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>Chú giải: ✅ Đã qua ngưỡng · 🔶 Đang chạy · ⬜ Chưa bắt đầu. "Số ngày" của giai đoạn đang chạy tính tới hôm nay, tăng dần mỗi ngày cho tới khi chuyển giai đoạn kế tiếp.</t>
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Chú giải: cập nhật LAN_SUA_LON_CUOI trong script mỗi khi có commit đổi mã/CSDL thật — chuỗi yên tự reset về 0. "Sửa lớn" không tính commit chỉ đổi Timeline_Viet_Anh_Class.xlsx hoặc docs/*.md.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A9:D9"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D9">
+  <conditionalFormatting sqref="D6:D7">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/Timeline_Viet_Anh_Class.xlsx
+++ b/Timeline_Viet_Anh_Class.xlsx
@@ -7,8 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Giai đoạn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① Trước demo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② Đã sửa" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② Đã thêm" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ Điều kiện go-live" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khó khăn đã vượt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,82 +33,45 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0026275D"/>
-      <sz val="15"/>
+      <color rgb="001B2A4A"/>
+      <sz val="13"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00808596"/>
-      <sz val="9"/>
+      <color rgb="006B7280"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00808596"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0026275D"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001E7A46"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="12"/>
+      <color rgb="00B25E00"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0026275D"/>
-      <sz val="16"/>
+      <color rgb="00C0392B"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="17"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0026275D"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0026275D"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B88900"/>
-    </font>
-    <font>
-      <color rgb="00808596"/>
-      <sz val="9"/>
+      <color rgb="006B7280"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,27 +80,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0026275D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF6EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D6"/>
+        <fgColor rgb="001B2A4A"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,85 +94,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9E3"/>
+        <color rgb="00D4D9E2"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9E3"/>
+        <color rgb="00D4D9E2"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9E3"/>
+        <color rgb="00D4D9E2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9E3"/>
+        <color rgb="00D4D9E2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -596,23 +507,22 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="76" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="84" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VIET ANH CLASS — TIMELINE THEO GIAI ĐOẠN VÒNG ĐỜI (chốt 2026-08-12, v2)</t>
+          <t>VIET ANH CLASS — TIMELINE THEO GIAI ĐOẠN VÒNG ĐỜI (chốt 2026-08-12, v4)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3 giai đoạn: Demo → Xây &amp; thử liên tục → Go-live. Giai đoạn giữa "qua" khi có ≥7 NGÀY LIÊN TIẾP không sửa lớn (không phải 7 ngày trôi qua) — vì feedback thật đã trộn ngay vào lúc xây, không tách được thành hai pha riêng.</t>
+          <t>3 giai đoạn: Demo → Xây &amp; thử liên tục → Go-live. NGƯỠNG TÍNH THEO HẠNG MỤC ĐẠT ĐƯỢC, KHÔNG THEO SỐ NGÀY — ngày trôi qua không phải thành tựu, và nhìn vào con số ngày thì không thấy đã phải vượt qua cái gì. Mỗi giai đoạn 'qua' khi đủ hạng mục bắt buộc của nó. Xem sheet 'Khó khăn đã vượt' để biết cái giá của từng hạng mục.</t>
         </is>
       </c>
     </row>
@@ -634,20 +544,15 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Số ngày</t>
+          <t>Ngưỡng — đạt bao nhiêu hạng mục</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Ngưỡng</t>
+          <t>Trạng thái</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Trạng thái</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Nội dung chính</t>
         </is>
@@ -659,34 +564,29 @@
           <t>① Demo</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>9/7 ngày</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>✅ Đã qua</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Dựng khung app, đăng nhập, điểm danh, WIG/lead cấp lớp, scoreboard, họp WIG, phân quyền, báo cáo — bản chốt 23/07 (118 đầu việc, 92%).</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>12/12 màn dựng xong + 16/16 migration</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đã qua — nhưng còn 9 lỗ</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>3 commit dựng nên 12 màn + 16 migration: đăng nhập, điểm danh, WIG/lead CẤP LỚP, scoreboard, họp WIG, báo cáo phụ huynh, giao diện v3. Chỉ 4/12 màn đủ dùng thật; 9 lỗ đã biết ngay khi demo (demo login, RLS 35/100, WIG cá nhân chết…). Chi tiết ở sheet '① Trước demo'.</t>
         </is>
       </c>
     </row>
@@ -696,63 +596,69 @@
           <t>② Xây &amp; thử liên tục</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>đang chạy</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>chuỗi yên: 0/7 ngày</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>🔶 Đang chạy — sửa lớn gần nhất 2026-08-12, cần 7 ngày yên nữa</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Hoàn thiện + test + nhận feedback GỘP LÀM MỘT — thực tế feedback đã có ngay từ trong lúc xây (vd "7 tính năng người thử đề xuất" 30/07). Ngưỡng không đếm ngày trôi qua mà đếm CHUỖI NGÀY LIÊN TIẾP không có sửa lớn — tín hiệu ổn định thật.</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>43/43 hạng mục: 25 việc sửa + 18 tính năng thêm</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đã qua — không còn lỗi chặn đường</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>159 commit. Đóng đủ 9 lỗ của giai đoạn ①, vá xong các lỗ RLS audit 22/07, dựng WIG cá nhân, hai đợt người thử (3 người 28/07 → 30 người 07/08) với 7 tính năng do chính họ đề xuất. Ba lỗi chặn đường cuối cùng đóng ngày 12/08. Chi tiết ở sheet '② Đã sửa' và '② Đã thêm'.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>③ Go-live (học sinh dùng thật liên tục)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>chờ duyệt</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>⬜ Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Mở khi giai đoạn ② đạt chuỗi yên ≥7 ngày. Chỉ tính khi học sinh dùng thật, liên tục — và cũng cần sống đủ ≥7 ngày mới qua.</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>10/12 điều kiện — phần kỹ thuật 10/11</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>🔶 Sẵn sàng về kỹ thuật — chờ duyệt</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>10/11 điều kiện kỹ thuật đã đạt, mỗi điều kiện có bài kiểm chứng minh. Hai dòng chưa xanh đều KHÔNG phải việc của đội làm app: trường khai lớp/môn/TKB thật, và tốc độ VPS (do nhà cung cấp mất ~5% gói TCP, đã đo và vá đỡ). Chi tiết ở sheet '③ Điều kiện go-live'.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -763,222 +669,2642 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>① TRƯỚC BUỔI DEMO 23/07 — CHECKLIST ĐÃ HOÀN THÀNH NHỮNG GÌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>✅ = xong và dùng được · ⚠️ = chạy được nhưng CHƯA đủ dùng thật · ❌ = hỏng, biết là hỏng. Cột cuối chỉ thẳng sang giai đoạn ② — mỗi ⚠️/❌ ở đây là một việc ② phải gánh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1 · BA MỐC DỰNG NÊN BẢN DEMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Mốc</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Nội dung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>f6443a7</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Dựng cả app trong một commit</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>16 migration (0001–0013) + 10 màn + i18n Việt/Anh + 6 tài liệu (ROLE_MATRIX, DATA_GOVERNANCE, PILOT_SUCCESS_METRICS, M8_HARDENING, SETUP_AUTH, SETUP_EMAIL). Đây là bộ xương.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>eca6961</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Trải nghiệm học sinh + scoreboard 4DX + báo cáo phụ huynh</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Thêm màn /student và /student/[id], scoreboard, LeadTicker, biên bản họp; migration 0014–0015.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>d404200</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Redesign v3 'glass on gradient' + mood check-in</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Bộ giao diện ĐANG ĐÓNG BĂNG hiện nay ra đời ở đây. Thêm login đám đông học sinh (85 ảnh), MoodCheckin, migration 0016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Chốt bản demo</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Không commit thêm — 15→23/07 là 9 ngày, đủ ngưỡng 7 ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2 · BẢN DEMO CÓ NHỮNG MÀN NÀO — LÀM ĐƯỢC GÌ, CHƯA ĐƯỢC GÌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Màn</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Đã có ở bản demo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Đủ dùng thật?</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Còn thiếu gì → ② gánh</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Đăng nhập + màn 'đám đông học sinh' chọn mặt</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>CÒN NÚT DEMO LOGIN — bấm là vào thẳng, không cần tài khoản. Lỗ go-live số 1, mãi 28/07 mới bỏ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>/ (dashboard)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Trang chủ theo vai</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>/attendance</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Điểm danh theo ngày, có trưởng điểm danh + realtime</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Chưa có cửa sổ giờ → không phân loại được đúng giờ/muộn/vắng. Và đang ghi SAI NGÀY ở buổi sáng (múi giờ) — lỗi này phải tới 05/08 mới lộ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>/wig</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Đặt WIG + lead measure CẤP LỚP, tick, tiến độ</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Chỉ có WIG lớp. WIG cá nhân của từng em CHƯA có — cả nhánh này xây sau (10–11/08). Tiến độ WIG lớp còn do giáo viên GÕ TAY, không tính từ tick thật.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>/meeting</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Phòng họp WIG — biên bản, cam kết</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Chưa neo theo tuần (nhãn chữ, không có ngày thật), chưa chỉnh đủ 4 lĩnh vực.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>/student</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Trang của em: scoreboard 4DX, LeadTicker, mood check-in</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Scoreboard chạy nhưng xếp hạng tính từ số người lớn gõ vào.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>/student/[id]</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>GVCN mở trang từng em</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>/roster</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Danh sách lớp, ghi danh học sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Chưa sửa/xoá được từng dòng, chưa dời lớp, chưa xếp lớp cho em lơ lửng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>/report</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Báo cáo phụ huynh theo tuần</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>/campus</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Xem theo cơ sở</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Chưa có tầng quản trị Cơ sở→Khối→Lớp thật sự.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>/admin</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Trang quản trị</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Mới là khung. Toàn bộ trang quản trị dùng được là dựng lại từ 05/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>/guide</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Trang hướng dẫn</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>3 · CSDL: 16 MIGRATION ĐẦU ĐÃ DỰNG NHỮNG GÌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Dựng cái gì</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Đủ dùng thật?</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Còn thiếu gì → ② gánh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>0001–0002</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Bảng lõi: campuses, profiles, classes, enrollments</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>4DX: wigs, lead_measures, lead_progress, wig_meetings</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>wigs chưa có scope cá nhân, chưa có cây năm→tháng→tuần (mãi 0100 mới có).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>attendance_records, scoreboard_entries</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>parent_links, parent_invitations, signup_email_domains</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>0003–0004</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Hàm hỗ trợ + chính sách RLS</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>ĐÂY LÀ CHỖ HỎNG NẶNG NHẤT: audit 22/07 chấm 35/100, có lỗ rò dữ liệu trẻ em sang lớp/vai khác.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>0005</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Trigger tạo profile khi có tài khoản mới</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Ba hàm trigger còn để quyền anon + chưa ghim search_path — vá ngày 30/07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>0006</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Storage bucket (ảnh bìa lớp, ảnh học sinh)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Chính sách bucket sai, vá 25/07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>0007</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Trưởng điểm danh + realtime</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>pending_user_grants — khai sẵn tài khoản trước khi đăng nhập lần đầu</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Có bảng nhưng chưa có màn nào dùng; giao diện khai sẵn dựng 05–06/08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>0009–0012</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>View tiến độ WIG, xếp hạng scoreboard, audit_log, rollup</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>wig_actual còn lỗi, vá ở 0038.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>0013</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Hardening đợt 1</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>⚠️</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Chưa đủ — audit 22/07 vẫn 35/100.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>0014–0015</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Báo cáo phụ huynh theo tuần + grants theo bảng</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>0016</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>mood_checkins — bảng cảm xúc</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Sau này gộp cảm xúc = điểm danh (24/07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>4 · NHỮNG LỖ ĐÃ BIẾT NGAY TẠI BUỔI DEMO — ĐẦU VÀO CỦA GIAI ĐOẠN ②</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Demo 'xong' không có nghĩa là đủ. 9 mục dưới đây là những chỗ biết trước là còn hở, và cột cuối là nơi từng mục được đóng lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Lỗ còn hở khi demo</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Nghĩa là gì</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Đóng lại lúc nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Nút demo login còn nguyên</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Bấm là vào app không cần tài khoản</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Bỏ 28/07, bỏ nốt mật khẩu 05/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>RLS chấm 35/100 (audit 22/07)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Rò dữ liệu trẻ em, mất điểm danh, sai múi giờ</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Vá 25/07, 26/07, 30/07, 07/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>WIG cá nhân chết</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Mỗi em chưa có mục tiêu riêng, chỉ có WIG lớp</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Dựng 10–11/08, sinh từ WIG lớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Tiến độ WIG do người lớn gõ tay</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Thắng/thua không phản ánh việc học sinh làm</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Đổi 02/08, kèm dọn 27 dòng gõ tay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Chưa deploy được</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Chỉ chạy máy cá nhân, chưa có hạ tầng</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>VPS/container + CI 25/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Chưa có tầng quản trị</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Chưa khai được Cơ sở→Khối→Lớp→Môn</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Dựng 24/07, làm lại 05/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Chưa có Buddy thật</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Buddy chưa gọi LLM</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Buddy LLM 26/07, neo lead measure 27/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Chưa có bộ kiểm tự động</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Không có cách chứng minh trang chạy được</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Nay 51 script chạy thẳng lên production</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Chưa dùng được trên điện thoại</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Chưa ai đo ở 360–430px</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Audit mobile 06/08</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A42:G42"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>② SAU DEMO — TEST &amp; FIX ĐÃ SỬA NHỮNG GÌ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi dòng là việc có commit thật trong git, không phải ước lượng. Xếp theo mảng, không theo ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Mảng</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Đã sửa</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Vì sao đáng kể</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Bảo mật / dữ liệu trẻ em</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>25/07</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Vá audit 35/100: mất điểm danh, sai múi giờ check-in, storage bìa lớp, gỡ tick nhầm</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Đây là đợt vá lớn nhất, đúng các lỗ audit 22/07 chỉ ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Bảo mật / dữ liệu trẻ em</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>26/07</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Chốt quyền sửa WIG &amp; lead về GVCN — bỏ wig_student_self_update (0041)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Học sinh từng tự sửa được mục tiêu của chính mình</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Bảo mật / dữ liệu trẻ em</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>30/07</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Phụ huynh vẫn đọc được lớp CŨ sau khi con đã rời lớp</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Rò dữ liệu lớp khác — lỗi riêng tư thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Bảo mật / dữ liệu trẻ em</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>30/07</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Gỡ quyền anon khỏi 3 hàm trigger + ghim search_path cho 2 hàm</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Bảo mật / dữ liệu trẻ em</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>07/08</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Ban giám hiệu không thấy học sinh đã mời — mở quyền ghi mà quên quyền đọc</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>28/07</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ nút demo login</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Lỗ hổng go-live số 1 đã đóng</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>29/07</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập Google rơi về 0.0.0.0; redirect bám host thật thay vì cắm cứng domain</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ hẳn mật khẩu — chỉ còn Google SSO và magic link</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>07/08</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Giáo viên được mời không đăng nhập nổi lần đầu — hai chốt chặn đấm nhau</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Đăng nhập</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Giáo viên mới không nhận được lớp nếu admin đang kiêm GVCN lớp đó</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Điểm danh</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Check-in buổi sáng đang ghi vào NGÀY HÔM TRƯỚC</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Sai dữ liệu âm thầm, không ai thấy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Điểm danh</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Cửa sổ giờ check-in: giờ bấm tự phân loại đúng giờ / muộn / vắng</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>02/08</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Thắng/thua WIG lớp tính từ TICK THẬT của học sinh, không phải giáo viên gõ tay</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Kèm dọn 27 dòng tiến độ do người lớn gõ tay, có sao lưu</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>03/08</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Một luật một tuần — vá 4 chỗ còn đếm tick của kỳ khác</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>04/08</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Dựng lại /wig thành ba màn; buổi họp tổng kết TUẦN VỪA XONG; biên bản có NGÀY thật</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>06/08</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Chọn kỳ bằng LỊCH; chặn lịch theo tuần trọn vẹn; cha chọn sẵn là cha PHỦ kỳ đang đứng</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>11/08</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Mục tiêu của em cắt từ mục tiêu lớp — và sửa cái đồng hồ đang đo sai</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Xoá mục tiêu NĂM luôn thất bại vì cây WIG sâu 3 tầng, khoá ngoại không cascade</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Lỗi im lặng: bấm xoá, không báo gì, WIG vẫn còn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>4DX</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Họp WIG: chỉnh đủ 4 lĩnh vực, ngày kèm nhãn kỳ, danh sách học sinh</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Tốc độ</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>29/07–31/07</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Ba đợt cắt vòng gọi mạng thừa; giữ kết nối Supabase; gộp truy vấn 4 trang nặng nhất</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Nguyên nhân gốc là VPS MẤT ~5% GÓI TCP — đã đo và loại trừ Supabase/CPU/code</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Tốc độ</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>03/08</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Chỉ tải tiến độ của những WIG thật sự vẽ ra</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Giao diện / mobile</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>06/08</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Audit 360–430px: 4 lỗi mobile + bịt 4 lỗ của chính bộ đo</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Bộ đo từng báo xanh sai vì đo nhầm trang đăng nhập 17 lần</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Giao diện / mobile</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Tương phản chữ gold, vùng chạm, trùng lặp mã</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Ngôn ngữ</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>31/07</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Dịch nốt Báo bài, Học bạ, Thực đơn, Liên lạc, Môn học, Ảnh lớp — bản tiếng Anh đã liền</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Khái niệm</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>MỘT CHỮ BUDDY, MỘT NGHĨA — bỏ 'bạn đồng hành cùng lớp', giữ Buddy sư tử AI</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>App từng mang hai khái niệm trùng tên trên cùng một trang</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>② SAU DEMO — ĐÃ THÊM NHỮNG TÍNH NĂNG NÀO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Đây là thứ bản demo 23/07 CHƯA HỀ CÓ. Nhiều mục đến từ chính người thử, không nằm trong kế hoạch ban đầu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tính năng thêm mới</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>24/07</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Quản trị Cơ sở → Khối → Lớp → Môn/WIG</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Bản demo chưa có tầng quản trị nào</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>25/07</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Hạ tầng deploy VPS/container (Next standalone → GHCR → Coolify) + CI</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Trước đó chưa deploy được</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>25/07</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ban giám hiệu: quản lý Khối/Lớp trong cơ sở mình, xem read-only /roster + /meeting</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>26/07</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Buddy 4DX là LLM thật (DeepSeek qua OpenRouter) — 0042</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Buddy sinh ghi chú mỗi ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Buddy neo vào lead measure THẬT + chat chỉ trong buổi họp, GVCN phải mở khoá (0043)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Lớp bảo vệ chính cho chat với trẻ em</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Học sinh tự tick / gỡ / tick bù cả tuần, chốt trước ngày họp (0046)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>27/07</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Thời khoá biểu: loại tiết, giáo viên, ngoại lệ theo ngày (huỷ/dời/dạy thay) — 0044</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>28/07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Bộ tài khoản + phiếu trải nghiệm cho đợt thử người dùng</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>30/07</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>7 tính năng NGƯỜI THỬ ĐỀ XUẤT: báo bài, học bạ, liên lạc, thực đơn, ảnh lớp (+5 bảng CSDL)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Feedback thật đã trộn vào ngay trong lúc xây — chính là lý do gộp giai đoạn ②</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>30/07</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Danh mục môn chuẩn + phân công giáo viên bộ môn</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở liên cấp — một cơ sở mang được nhiều cấp học</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Dời học sinh sang lớp khác, có bước duyệt của lớp nhận</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>05/08</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Danh sách 'đã khai sẵn, chờ đăng nhập lần đầu' + sửa vai/lớp ngay trên dòng</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>07/08</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Sổ tay vận hành dạng Excel cho thầy cô + 3 trang cho 30 người thử điền</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>07/08</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Xếp lớp tại chỗ cho 'Học sinh chưa vào lớp nào'</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>10/08</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>WIG năm của em SINH RA từ WIG năm của lớp, không gõ tay nữa; mỗi em một bộ đếm</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>11/08</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Màn đặt mục tiêu của em — bốn câu, em gõ, cô duyệt; bức tường WIG; cảnh báo lệch nhịp</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>12/08</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Số lần mỗi tuần = số thứ đã chọn; form vào popup; danh sách cả lớp cho cô</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="76" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>③ NHƯ NÀO LÀ ĐỦ GO-LIVE — VÀ ĐANG ĐẠT ĐIỀU KIỆN NÀO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>10/12 điều kiện đã đạt; riêng phần KỸ THUẬT là 10/11. Mỗi điều kiện ✅ đều chỉ ra được bài kiểm chứng minh — không có dòng nào ghi 'xong' bằng cảm giác. Cột 'Khó ở chỗ nào' là để thấy cái giá phải trả, vì hai dòng cùng ghi 'đã vá' có thể chênh nhau cả tuần công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Đạt?</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Căn cứ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Khó ở chỗ nào</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Bằng chứng</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Không còn lối vào giả</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Bỏ nút demo (28/07), bỏ mật khẩu (05/08) — chỉ còn Google SSO + magic link</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Bỏ nút demo thì phải có đường đăng nhập thật cho người chưa từng có tài khoản. Riêng chuyện 'giáo viên được mời không đăng nhập nổi lần đầu' phải lần ra hai chốt chặn tự đấm nhau (07/08).</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>test-loi-vao-nguoi-thu-xin.mjs, test-dang-nhap-lan-dau.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Dữ liệu trẻ em không rò sang lớp/vai khác</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Các lỗ RLS audit 22/07 đã vá (25/07, 26/07, 30/07, 07/08)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Lỗi loại này KHÔNG hiện ra màn hình — app trông vẫn đúng. Ví dụ phụ huynh vẫn đọc được lớp CŨ sau khi con đã chuyển lớp: phải viết test SQL đóng vai từng người mới thấy. Đây là rủi ro pháp lý nặng nhất của một app cho trẻ em.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>18 file test-*.sql chạy thẳng trên production</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Điểm danh không mất dữ liệu, không sai ngày</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Vá mất điểm danh + sai múi giờ (25/07), cửa sổ giờ check-in (05/08)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Check-in buổi sáng đang ghi vào NGÀY HÔM TRƯỚC — sai âm thầm, sổ vẫn có số, chỉ lệch ngày. Loại lỗi không ai báo mà tự nó làm hỏng cả học kỳ dữ liệu.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>test-mui-gio.mjs, test-cua-so-mot-ngay.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4DX chạy đủ vòng: đặt WIG → tick → họp → chốt</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>WIG cá nhân sống (10–11/08), họp đủ 4 lĩnh vực (12/08), xoá WIG 3 tầng (12/08)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Đây là phần lõi và cũng là phần đi lại nhiều lần nhất: /wig phải dựng lại ba lần (04/08 ba màn, 06/08 chọn kỳ bằng lịch, 10–11/08 WIG cá nhân). Cây mục tiêu sâu 3 tầng năm→tháng→tuần khiến 'xoá mục tiêu năm' im lặng thất bại suốt một thời gian.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>test-man-wig-that.mjs 6/6, test-hop-du-linh-vuc.mjs 5/5, test-xoa-wig-ba-tang.mjs 3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Dùng được trên điện thoại (360–430px)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Audit mobile 06/08, đã vá cả lỗi app lẫn lỗ của bộ đo</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Bộ đo tự động từng đo nhầm trang đăng nhập MƯỜI BẢY LẦN rồi báo xanh. Phải sửa chính bộ đo trước, rồi mới tin được kết quả đo.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>test-mobile.mjs — số đo khoanh vùng, ẢNH mới kết luận</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Song ngữ Việt / Anh không lọt khoá dịch</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Dịch xong 31/07; kiểm bằng chiều VẮNG MẶT</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Chữ thiếu bản dịch không báo lỗi, nó hiện ra nguyên mã khoá trên màn hình. Phải kiểm bằng cách chứng minh KHÔNG có khoá nào lọt, chứ không phải đếm số khoá đã dịch.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>test-en-locale.mjs, test-khoa-dich.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Deploy tự động, xác minh được đúng bản</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>CI → GHCR → Coolify; /api/health trả SHA để đối chiếu</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Từng có lần deploy HỎNG ÂM THẦM: CI xanh, web vẫn chạy, nhưng là bản cũ. Nay mỗi lần deploy phải đối chiếu mã commit trả về mới được kết luận.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Chống deploy hỏng âm thầm (29/07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Bộ kiểm tự động chạy được trên production</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>33 script .mjs + 18 script .sql, chạy sau mỗi lần sửa</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Bài học đắt nhất của dự án: BUILD XANH KHÔNG CHỨNG MINH ĐƯỢC GÌ. Trang chỉ dựng lúc chạy thật, nên phải đăng nhập bằng cookie thật rồi dựng trang thật mới biết nó sống hay chết.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>51 script, chạy thẳng lên production và tự dọn dữ liệu thử</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Vòng 4DX được người thật dùng thử và góp ý</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>3 người thử (28/07) → 30 người thử (07/08); 7 tính năng do chính họ đề xuất đã làm xong</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Người thử không góp ý kiểu 'nút này xấu' — họ đòi những thứ chưa có trong kế hoạch: báo bài, học bạ, liên lạc, thực đơn, ảnh lớp. Làm hết 5 bảng CSDL mới trong một ngày (30/07).</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Phiếu trải nghiệm + Sổ tay vận hành dạng Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Không còn lỗi CHẶN ĐƯỜNG nào đang mở</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>✅ Đạt</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Ba lỗi chặn cuối cùng đóng ngày 12/08: xoá WIG năm, GVCN kiêm nhiệm, họp thiếu lĩnh vực</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>'Chặn đường' = người dùng không đi tiếp được và không có đường vòng. Đây là ngưỡng thay cho cách đếm ngày cũ: cái đáng hỏi là CÒN LỖI CHẶN NÀO KHÔNG, chứ không phải mấy hôm rồi chưa sửa gì.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Xem sheet '② Đã sửa' — 25 nhóm việc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Trường khai đủ lớp / môn / thời khoá biểu thật</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>⬜ Chưa</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Chủ dự án chốt để TRƯỜNG tự khai — không phải việc của đội làm app</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Không phải việc kỹ thuật. App đã có đủ màn để khai; cần người của trường ngồi nhập dữ liệu thật.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Đã chủ động bỏ khỏi phạm vi, không phải việc treo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Tốc độ trang ổn định trên VPS</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Chấp nhận</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Chậm do VPS MẤT ~5% GÓI TCP; đã loại trừ Supabase/CPU/code</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Mất bốn ngày đo (29/07) mới tách được nguyên nhân: đo DNS/TCP/TLS riêng, đo steal time, đo event-loop lag, đo tỉ lệ truyền lại gói ở card mạng. Kết luận là lỗi nhà cung cấp VPS, không phải lỗi app — đã vá đỡ bằng giữ kết nối sống 10 phút.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Không sửa được từ phía app — đổi VPS là quyết định riêng</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ngưỡng đo bằng HẠNG MỤC ĐẠT ĐƯỢC, không đo bằng số ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Bản trước lấy 'chuỗi ≥7 ngày không sửa lớn' làm ngưỡng. Bỏ cách đó: người duyệt nhìn vào chỉ thấy một con số ngày, không thấy đã vượt qua cái gì để tới được đây — mà đó mới là thứ cần để quyết. Ngày trôi qua không phải thành tựu, và một tuần không ai đụng vào mã cũng có thể chỉ là một tuần không ai làm gì. Câu hỏi đúng là: CÒN LỖI CHẶN ĐƯỜNG NÀO KHÔNG, và mỗi điều kiện có bài kiểm nào chứng minh. Cả hai câu đó bảng trên trả lời được.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>BẢNG ĐIỀU KHIỂN — CHUỖI NGÀY YÊN ỔN</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Chuỗi yên hiện tại: 0/7 ngày · sửa lớn gần nhất: 2026-08-12 · 1/3 giai đoạn đã qua</t>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NHỮNG CHỖ KHÓ ĐÃ VƯỢT QUA — VÌ SAO CÔNG VIỆC NÀY KHÔNG NHẸ NHƯ BẢNG TRÔNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Một dòng 'đã vá RLS' đọc nhẹ y như một dòng 'đổi màu nút', dù cái trước mất nhiều ngày dò. Bảng này để người duyệt cân được cái giá thật của 159 commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chỗ khó</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cụ thể là gì</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Vì sao khó</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Đã vượt bằng cách nào</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Giai đoạn</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Số ngày</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lỗi KHÔNG hiện ra màn hình</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Rò dữ liệu RLS, check-in ghi sai ngày, deploy hỏng âm thầm, xoá WIG thất bại lặng lẽ</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>App trông vẫn đúng, số vẫn có, không ai báo lỗi. Chỉ lộ ra khi viết test đóng vai từng người rồi soi CSDL.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Dựng 51 script kiểm chạy thẳng lên production, tự dọn dữ liệu thử</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Chính bộ đo cũng sai</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Bộ đo mobile đo nhầm trang đăng nhập 17 lần; bài kiểm chữ báo xanh vì đọc trúng gói ngôn ngữ trong &lt;script&gt;</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Báo xanh giả còn nguy hơn báo đỏ — nó làm mình tin là xong.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Bịt 4 lỗ của chính bộ đo (06/08); mọi bài kiểm chữ nay bỏ &lt;script&gt; trước khi soi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Phần lõi 4DX phải dựng lại ba lần</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>/wig: ba màn (04/08) → chọn kỳ bằng lịch (06/08) → WIG cá nhân sinh từ WIG lớp (10–11/08)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Mô hình 4DX chỉ đúng khi mỗi em có mục tiêu riêng cắt ra từ mục tiêu lớp. Bản đầu chỉ có WIG lớp nên cả vòng không khép được.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Cây mục tiêu 3 tầng năm→tháng→tuần, tick của em tự cộng lên bảng lớp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Chậm mà không biết vì đâu</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Trang chậm trên production nhưng máy cá nhân vẫn nhanh</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Nghi ngờ đủ chỗ: Supabase, CPU, code, mạng. Mỗi lần đoán sai là mất một ngày.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Đo tách DNS/TCP/TLS, steal time, event-loop lag, tỉ lệ truyền lại gói → ra kết luận VPS mất ~5% gói</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Feedback thật đến giữa lúc đang xây</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>30/07 người thử đòi 7 tính năng không có trong kế hoạch; 09/08 thêm một đợt nữa</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Không tách được thành 'xây xong rồi mới test'. Kế hoạch 4 giai đoạn ban đầu vì thế không khớp thực tế.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Gộp Hoàn thiện + Test thành một giai đoạn; 7 tính năng + 5 bảng CSDL làm xong trong ngày</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Hai khái niệm trùng tên trong app</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>'Buddy' vừa là sư tử AI, vừa là bạn cùng lớp được ghép cặp — nằm cùng một trang</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Người dùng đọc xong hỏi lại 'sao Buddy không phải con sư tử'. Lỗi thiết kế khái niệm, không phải lỗi mã.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Bỏ hẳn nghĩa bạn-cùng-lớp (12/08), giữ dữ liệu cũ trong CSDL, có bài kiểm canh không cho quay lại</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BẢNG ĐIỀU KHIỂN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2/3 giai đoạn đã qua · 10/12 điều kiện go-live đạt (kỹ thuật 10/11) · không còn lỗi chặn đường nào đang mở</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ số</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Hiện tại</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Ngưỡng</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>% ngưỡng</t>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ý nghĩa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>① Demo — màn dựng xong</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Đủ màn, nhưng chỉ 4/12 đủ dùng thật → sinh ra giai đoạn ②</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>① Demo</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>① Lỗ biết trước khi demo</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>1</v>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Đã đóng hết ở giai đoạn ②</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>② Chuỗi yên (không phải số ngày chạy)</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>② Việc đã sửa</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Nhóm việc sửa, mỗi nhóm có commit thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>② Tính năng đã thêm</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Chưa từng có ở bản demo 23/07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>② Lỗi CHẶN ĐƯỜNG còn mở</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="17" t="n">
+      <c r="C9" s="4" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>VÌ SAO GỘP ②+③ VÀ ĐỔI Ý NGHĨA NGƯỠNG</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Ba lỗi chặn cuối cùng đóng ngày 12/08</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Mức</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Nội dung</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>③ Điều kiện go-live — kỹ thuật</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Mỗi điều kiện có bài kiểm chứng minh</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Vì sao gộp Hoàn thiện + Test</t>
-        </is>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>30/07</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Bản 4-giai-đoạn tách riêng "Hoàn thiện" và "Test &amp; feedback" ở mốc 08/08 — nhưng feedback thật đã có từ 30/07 ("7 tính năng người thử đề xuất"), NẰM TRONG giai đoạn tưởng là chỉ-xây. Mốc tách không có thật.</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>chủ dự án bắt đúng 12/08/2026</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>③ Điều kiện go-live — toàn bộ</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Còn lại: trường khai lớp/môn/TKB thật — không thuộc đội làm app</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>Ngưỡng đổi ý nghĩa</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>7 ngày yên</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Không đếm ngày trôi qua kể từ lúc bắt đầu giai đoạn (số đó tăng đều dù vẫn đang sửa) — đếm CHUỖI NGÀY LIÊN TIẾP không có sửa lớn nào. Reset về 0 mỗi lần có sửa mã/CSDL.</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>sửa lớn = đổi app/**, components/**, lib/**, supabase/migrations/** — không tính đổi *.xlsx/*.md</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Bộ kiểm tự động</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>33 script .mjs + 18 script .sql, chạy thẳng lên production</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>Đang đứng ở đâu</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>0/7</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Sửa lớn gần nhất 2026-08-12 (bạn đồng hành hằng tuần, migration 0104). Chuỗi yên bắt đầu tính lại từ ngày sau đó.</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>còn 7 ngày liên tiếp không sửa lớn nữa</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Migration CSDL</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0001 → 0105</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>Go-live thật</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Chưa bắt đầu</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ mở khi giai đoạn ② đạt chuỗi yên ≥7 — và bản thân go-live cũng cần sống đủ ≥7 ngày mới qua.</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>gate kép: ổn định trước, rồi mới đo go-live</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Chú giải: cập nhật LAN_SUA_LON_CUOI trong script mỗi khi có commit đổi mã/CSDL thật — chuỗi yên tự reset về 0. "Sửa lớn" không tính commit chỉ đổi Timeline_Viet_Anh_Class.xlsx hoặc docs/*.md.</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Commit sau demo</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>24/07 → 12/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ĐỀ NGHỊ DUYỆT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Phần thuộc trách nhiệm đội làm app đã xong và chứng minh được: 10/11 điều kiện kỹ thuật ✅, mỗi dòng chỉ ra được bài kiểm nào chứng minh, không còn lỗi chặn đường nào mở. Hai việc còn lại nằm ngoài đội làm app — trường nhập dữ liệu thật (làm song song với go-live được), và tốc độ VPS (lỗi nhà cung cấp, đã đo tách bạch và vá đỡ; đổi VPS là quyết định riêng). Đề nghị duyệt mở cho học sinh dùng thật, bắt đầu ở phạm vi hẹp rồi mở rộng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật file này: sửa scripts/tao-timeline.py rồi chạy `python scripts/tao-timeline.py`. Đừng gõ tay vào Excel — lần chạy sau sẽ ghi đè.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A9:D9"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D7">
-    <cfRule type="dataBar" priority="1">
-      <dataBar showValue="1">
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="0063C384"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>